--- a/artfynd/A 35200-2021 artfynd.xlsx
+++ b/artfynd/A 35200-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35200-2021 artfynd.xlsx
+++ b/artfynd/A 35200-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100859645</v>
+        <v>100859643</v>
       </c>
       <c r="B2" t="n">
-        <v>6202</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105336</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,16 +708,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gillbonderyd 3, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537296.9617048057</v>
+        <v>537362</v>
       </c>
       <c r="R2" t="n">
-        <v>6309033.213709979</v>
+        <v>6309032</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -752,24 +752,9 @@
           <t>2022-05-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>U bark på granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,6 +783,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100859645</v>
+      </c>
+      <c r="B3" t="n">
+        <v>6274</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gillbonderyd 3, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>537296</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6309033</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>U bark på granlåga</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
